--- a/data/trans_dic/P32A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,77</t>
+          <t>0,39; 2,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,79</t>
+          <t>0,67; 3,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,26</t>
+          <t>0,71; 3,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,34</t>
+          <t>0,57; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,58</t>
+          <t>0,58; 6,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,96</t>
+          <t>0,17; 2,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,05</t>
+          <t>0,93; 3,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,74</t>
+          <t>0,7; 2,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,42</t>
+          <t>0,58; 2,49</t>
         </is>
       </c>
     </row>
@@ -857,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,09</t>
+          <t>0,33; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,84</t>
+          <t>0,93; 4,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,7</t>
+          <t>1,75; 4,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,14</t>
+          <t>0,86; 3,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,46</t>
+          <t>0,29; 2,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,05</t>
+          <t>1,2; 5,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,83</t>
+          <t>0,72; 2,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,34</t>
+          <t>1,32; 3,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,29</t>
+          <t>1,26; 3,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,21</t>
+          <t>1,01; 4,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,97</t>
+          <t>2,06; 5,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,8</t>
+          <t>0,96; 4,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,96</t>
+          <t>0,47; 3,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,03; 4,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,48</t>
+          <t>0,85; 3,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,09</t>
+          <t>1,34; 4,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,64</t>
+          <t>0,68; 2,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,75</t>
+          <t>0,29; 2,62</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,29</t>
+          <t>0,16; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,77</t>
+          <t>1,86; 4,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,82</t>
+          <t>0,63; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,25</t>
+          <t>1,28; 4,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,32</t>
+          <t>0,24; 3,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,46</t>
+          <t>1,01; 4,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,33</t>
+          <t>0,41; 2,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,2</t>
+          <t>0,22; 1,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,41</t>
+          <t>1,44; 3,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,72</t>
+          <t>1,05; 2,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,04</t>
+          <t>1,17; 2,99</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,65</t>
+          <t>0,64; 1,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,41</t>
+          <t>1,88; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,7</t>
+          <t>1,44; 2,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,46</t>
+          <t>1,23; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,68</t>
+          <t>0,39; 1,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,3</t>
+          <t>0,77; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,4</t>
+          <t>0,59; 2,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,23</t>
+          <t>0,55; 1,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,6</t>
+          <t>1,46; 2,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,24</t>
+          <t>1,31; 2,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,18</t>
+          <t>1,1; 2,14</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1073; 12163</t>
+          <t>1728; 12531</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2570; 11891</t>
+          <t>2842; 12962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2414; 14002</t>
+          <t>3040; 14950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2014; 11129</t>
+          <t>1896; 10731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1028; 9793</t>
+          <t>1022; 10542</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6963</t>
+          <t>0; 8017</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1077; 12142</t>
+          <t>1076; 13509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5879; 18340</t>
+          <t>5610; 19194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4379; 16851</t>
+          <t>4306; 17116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3029; 11936</t>
+          <t>2841; 12286</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1960; 12172</t>
+          <t>1937; 11131</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5710; 22739</t>
+          <t>5520; 24177</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9322; 27015</t>
+          <t>10059; 26683</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3903; 14992</t>
+          <t>4094; 15333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 5377</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>940; 7949</t>
+          <t>947; 9039</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2366; 12152</t>
+          <t>2408; 12022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1906; 11182</t>
+          <t>1913; 11181</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6522; 25127</t>
+          <t>6407; 25371</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12164; 30008</t>
+          <t>11823; 30812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8094; 22306</t>
+          <t>8516; 22429</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2921; 13929</t>
+          <t>3345; 15412</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8633; 27424</t>
+          <t>9452; 27328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4098; 16124</t>
+          <t>4090; 16984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1182; 9521</t>
+          <t>1510; 10122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5157</t>
+          <t>0; 6954</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5855</t>
+          <t>0; 5388</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 14851</t>
+          <t>93; 16252</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4589; 16049</t>
+          <t>3916; 16097</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9174; 27304</t>
+          <t>8963; 27535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4390; 17243</t>
+          <t>4438; 17713</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2341; 18959</t>
+          <t>2010; 18044</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>848; 6825</t>
+          <t>844; 7127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10978; 26596</t>
+          <t>10343; 26046</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3815; 16139</t>
+          <t>3584; 15090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6119; 18792</t>
+          <t>5673; 18665</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7201</t>
+          <t>0; 6174</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>924; 12116</t>
+          <t>888; 11291</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3960; 18133</t>
+          <t>4123; 17321</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1408; 6723</t>
+          <t>1198; 6662</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1760; 10029</t>
+          <t>1861; 10522</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13941; 31424</t>
+          <t>13277; 32062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10149; 26689</t>
+          <t>10282; 27364</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8836; 22240</t>
+          <t>8554; 21849</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12904; 30978</t>
+          <t>11965; 29959</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37804; 69413</t>
+          <t>38180; 69394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27273; 54016</t>
+          <t>28847; 55342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19920; 38761</t>
+          <t>19406; 39309</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>924; 7924</t>
+          <t>920; 7988</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4015; 17596</t>
+          <t>4072; 18124</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8583; 26333</t>
+          <t>8814; 24966</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6208; 24462</t>
+          <t>6027; 24138</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15185; 34160</t>
+          <t>15277; 35166</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44321; 79962</t>
+          <t>45046; 78254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41469; 70542</t>
+          <t>41155; 71005</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29711; 56615</t>
+          <t>28537; 55541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,85</t>
+          <t>0,24; 2,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,04</t>
+          <t>0,64; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,48</t>
+          <t>0,56; 3,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,22</t>
+          <t>0,58; 2,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,27 +742,27 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,01</t>
+          <t>0,58; 5,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,18</t>
+          <t>0,18; 1,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,19</t>
+          <t>0,9; 3,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,49</t>
+          <t>0,53; 2,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,91</t>
+          <t>0,33; 2,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,08</t>
+          <t>0,96; 3,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,64</t>
+          <t>1,71; 4,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,22</t>
+          <t>0,72; 2,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,8</t>
+          <t>0,29; 2,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,98</t>
+          <t>1,24; 6,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,3</t>
+          <t>0,22; 1,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,85</t>
+          <t>0,73; 2,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,43</t>
+          <t>1,37; 3,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,31</t>
+          <t>1,18; 3,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,66</t>
+          <t>1,1; 4,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,95</t>
+          <t>1,92; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,01</t>
+          <t>0,93; 3,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,15</t>
+          <t>0,74; 3,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,41</t>
+          <t>0,96; 8,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,49</t>
+          <t>0,87; 3,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,13</t>
+          <t>1,4; 4,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,71</t>
+          <t>0,65; 2,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,62</t>
+          <t>1,24; 4,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,35</t>
+          <t>0,16; 1,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,67</t>
+          <t>1,85; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,63</t>
+          <t>0,64; 2,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,22</t>
+          <t>1,33; 4,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,09</t>
+          <t>0,25; 3,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,26</t>
+          <t>0,94; 4,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,31</t>
+          <t>0,73; 4,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,26</t>
+          <t>0,21; 1,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,48</t>
+          <t>1,42; 3,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,79</t>
+          <t>1,03; 2,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,99</t>
+          <t>1,3; 3,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,59</t>
+          <t>0,66; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,41</t>
+          <t>1,92; 3,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,77</t>
+          <t>1,39; 2,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,5</t>
+          <t>1,26; 2,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,74</t>
+          <t>0,37; 1,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,18</t>
+          <t>0,73; 2,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,37</t>
+          <t>1,3; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,27</t>
+          <t>0,55; 1,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,54</t>
+          <t>1,5; 2,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,26</t>
+          <t>1,29; 2,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,14</t>
+          <t>1,48; 2,55</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6337</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1728; 12531</t>
+          <t>1074; 11754</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2842; 12962</t>
+          <t>2712; 13002</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3040; 14950</t>
+          <t>2415; 14257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1896; 10731</t>
+          <t>2041; 10225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1022; 10542</t>
+          <t>1020; 9710</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8017</t>
+          <t>0; 8027</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1076; 13509</t>
+          <t>1084; 12202</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5610; 19194</t>
+          <t>5421; 18946</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4306; 17116</t>
+          <t>4277; 17097</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2841; 12286</t>
+          <t>2779; 11955</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>14391</t>
         </is>
       </c>
     </row>
@@ -1853,22 +1853,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1937; 11131</t>
+          <t>1915; 11807</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5520; 24177</t>
+          <t>5667; 23118</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10059; 26683</t>
+          <t>9841; 26323</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4094; 15333</t>
+          <t>3607; 14245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,37 +1878,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5377</t>
+          <t>0; 5018</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>947; 9039</t>
+          <t>948; 9179</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2408; 12022</t>
+          <t>2778; 14289</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1913; 11181</t>
+          <t>1916; 10974</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6407; 25371</t>
+          <t>6458; 24611</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11823; 30812</t>
+          <t>12262; 29795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8516; 22429</t>
+          <t>8519; 22862</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>12341</t>
         </is>
       </c>
     </row>
@@ -2061,27 +2061,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3345; 15412</t>
+          <t>3656; 14414</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9452; 27328</t>
+          <t>8809; 27108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4090; 16984</t>
+          <t>3934; 15971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1510; 10122</t>
+          <t>2620; 12474</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6954</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2091,32 +2091,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5388</t>
+          <t>0; 5782</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93; 16252</t>
+          <t>1868; 15764</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3916; 16097</t>
+          <t>4032; 15206</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8963; 27535</t>
+          <t>9312; 27210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4438; 17713</t>
+          <t>4228; 16581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2010; 18044</t>
+          <t>6780; 22640</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>16741</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>844; 7127</t>
+          <t>851; 6970</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10343; 26046</t>
+          <t>10323; 26708</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3584; 15090</t>
+          <t>3690; 15659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5673; 18665</t>
+          <t>6167; 18702</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6174</t>
+          <t>0; 6992</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>888; 11291</t>
+          <t>896; 12318</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4123; 17321</t>
+          <t>3824; 17137</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1198; 6662</t>
+          <t>2245; 13321</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1861; 10522</t>
+          <t>1765; 10738</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13277; 32062</t>
+          <t>13058; 30930</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10282; 27364</t>
+          <t>10090; 27293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8554; 21849</t>
+          <t>10050; 28051</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11965; 29959</t>
+          <t>12346; 29693</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38180; 69394</t>
+          <t>39128; 70569</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28847; 55342</t>
+          <t>27913; 53413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19406; 39309</t>
+          <t>21105; 42024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>920; 7988</t>
+          <t>924; 8006</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4072; 18124</t>
+          <t>3822; 17226</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8814; 24966</t>
+          <t>8363; 24760</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6027; 24138</t>
+          <t>11687; 30924</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15277; 35166</t>
+          <t>15380; 35509</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45046; 78254</t>
+          <t>46237; 80252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41155; 71005</t>
+          <t>40566; 71659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28537; 55541</t>
+          <t>37978; 65653</t>
         </is>
       </c>
     </row>
